--- a/光伏配储项目/电价数据/2026/帅乡站.xlsx
+++ b/光伏配储项目/电价数据/2026/帅乡站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.42613</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.79064</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.47196</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.49324</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44122</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.36553</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.39728</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.41544</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24417</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.12888</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.01055</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.07031</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.07415000000000001</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.05968</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29342</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51467</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5598</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.74249</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14586</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.38232</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43399</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44079</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6678200000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.89238</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.50243</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21666</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.35031</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17348</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.04118</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.31205</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.41382</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45605</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.75975</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.13198</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95209</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.91154</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80775</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.77016</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51966</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49056</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47063</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42114</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43147</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.73294</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.90928</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.97435</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51374</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.54292</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.52111</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.52125</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50251</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40802</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48298</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.5228200000000001</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.48743</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.51663</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.65736</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.55741</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.52835</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.55641</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.57675</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4951</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.1735</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.01676</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.55523</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.18322</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.00356</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.02969</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60527</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.77213</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.80424</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.19177</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.41795</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.14378</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.86497</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.23153</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.27939</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.03444</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.11229</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.67088</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00573</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9291799999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.98345</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.82163</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.88322</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7413</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45533</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.71663</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7561100000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45489</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43296</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44892</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33549</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5015299999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50118</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45283</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42128</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45606</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48737</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45129</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22732</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8013899999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44709</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43556</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.32845</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62975</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.66913</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47016</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.45019</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.54653</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.47185</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.63932</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50893</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6308400000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.56584</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56133</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.74054</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.60693</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5089</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.5356300000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46211</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34301</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5244500000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51114</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4457</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45959</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42218</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.59776</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21899</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.19203</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6433300000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45551</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41208</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.54062</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47749</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5283300000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45111</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47517</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.48469</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.4966</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5832200000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.46917</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.5916699999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.52503</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49688</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5044999999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.44894</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42631</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42828</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33185</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28612</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.25874</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.04807</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13299</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.0384</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.03597</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.03796</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.42262</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.43392</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43898</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48834</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.54879</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3727</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.57838</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.53671</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.5538</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.44037</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.62362</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.43343</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10154</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04281</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.005679999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19793</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04514</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14071</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01133</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05207</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38434</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34808</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33446</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.43367</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46045</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78573</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86971</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6123200000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45128</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.43223</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45655</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.45919</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.67345</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.50691</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.63362</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.8225</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8911100000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47626</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.67157</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.50524</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.06457</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8125800000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8835599999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.51935</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.9129299999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.84878</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60062</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47955</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.48371</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5449299999999999</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.42979</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37277</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93477</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5332899999999999</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47926</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4601</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.55696</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.42607</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.47276</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.47199</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41803</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.10567</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.26129</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.03681</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25603</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27376</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.14702</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20393</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.46046</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.54439</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43563</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.48487</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.48641</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.47207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.79886</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.44418</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.97254</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.52223</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.24262</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.75048</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.84421</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.7004</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.82237</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.61177</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.48915</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.54132</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.47632</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.51003</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.45187</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.44355</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.48848</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.62493</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.46663</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.49012</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.46505</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.5195</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.55662</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.42499</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.52749</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4424</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43261</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.5198400000000001</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.47967</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.46961</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.63774</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.5719299999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25522</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16038</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01179</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26896</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26518</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.42037</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.66146</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.5595399999999999</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.03621</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.5642200000000001</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.52928</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.5198200000000001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.37707</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.52724</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.46022</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.41923</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.41374</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.43802</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.43804</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.55365</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.52212</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.56438</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.45355</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.5410900000000001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.50469</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.42055</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.25878</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.02458</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.01556</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.00273</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.20215</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.01229</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25784</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.01323</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.03726</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.06087</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.03804</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.22228</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.43559</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42867</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45829</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.44328</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.55013</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.47108</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.46079</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.54774</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.5345299999999999</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.53018</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.53664</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46259</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42615</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.4137</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41888</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.41246</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.39219</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.6852200000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.5708799999999999</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.48612</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.42673</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.44554</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.54691</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41879</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.43213</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23749</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25915</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18646</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1445</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18153</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.13743</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21702</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24439</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.20358</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.50591</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.41434</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.55111</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.4344</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.48654</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.44024</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42666</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.43355</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39584</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.40341</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.63773</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.6450900000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.42175</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.41456</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.4606</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.1566</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.45412</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.70305</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.53589</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.50645</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.46422</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.50327</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.54087</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26735</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26876</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.22418</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.6247999999999999</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.51842</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41327</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.48844</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.45155</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.45912</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.62727</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.51108</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5016499999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.48288</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.75186</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.42087</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.28107</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>1.06261</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.89922</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.41437</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.54971</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.44183</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.92988</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.49469</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.41507</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.52049</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.43815</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.42224</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.42197</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.44667</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.46979</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.44029</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.40277</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.40204</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.43246</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.55836</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.48481</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.46269</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.45785</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.45708</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.50093</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.48239</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.56877</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.5179400000000001</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.53912</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.46437</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.37968</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.41821</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.7363500000000001</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.41351</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.45547</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.40628</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.43697</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.46338</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.44467</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.5277500000000001</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.45405</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.68502</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.30319</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.5653400000000001</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.43984</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.60342</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.39212</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.41928</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.40868</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.38624</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.40761</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.42129</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25145</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.04098</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.17552</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.01085</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27481</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20818</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.05754</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15714</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21747</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20441</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27306</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.25213</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.26889</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.38949</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.43272</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.50648</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.5978600000000001</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.5701799999999999</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50115</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6919</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.64962</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.68059</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.6635800000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8559600000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.6373300000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.23735</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.72856</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5361900000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.45661</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.49553</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.61718</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.50488</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.39014</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.73068</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.63479</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.91053</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.47977</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.45679</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.47134</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.47964</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.44955</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.46042</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.48988</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.48691</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.44331</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47374</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46324</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.47933</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.46841</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.56098</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.5488</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.7343999999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.62646</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.54201</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.61561</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.5380499999999999</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47469</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.4358</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45492</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.49144</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.50843</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57267</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.41993</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.48143</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.45927</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.44309</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40598</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65711</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.13166</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.44322</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.19778</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.41551</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42576</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.51046</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.60081</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.53944</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.64015</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.64258</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.7091799999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.18429</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.30111</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.93657</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.1091</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.93245</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.71717</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.1522</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78737</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.64142</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6916599999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.5855900000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.60392</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5905</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.5785800000000001</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.5702999999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.6985399999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.49762</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.52067</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5457000000000001</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45373</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.53055</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4354</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.45535</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.57853</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.46987</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.47888</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.43697</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41757</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.62374</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.45841</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.46019</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.44283</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.26541</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.42524</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02648</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.59105</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.45816</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5266000000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.44647</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.21867</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.03349</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.03793999999999999</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.24822</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.43292</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.44706</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.41037</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.49624</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.47622</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43677</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.48988</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42734</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.47485</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.49982</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.5109</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.52711</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.50354</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.47466</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.5155299999999999</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.42521</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.49241</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.53426</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.5146900000000001</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.47275</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.6278400000000001</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.50891</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.5016</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.48519</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.48432</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.47033</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.6285599999999999</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41968</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.59768</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.59172</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.60565</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.44171</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.46935</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.56663</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.44554</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.46375</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.55132</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.47025</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.5495099999999999</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.4963</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.42604</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.56628</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.25736</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.22517</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.06728000000000001</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27044</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.11319</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.12308</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.23247</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.13451</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.07128</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.03974</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.01748</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27603</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.06915</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.20165</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.12472</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.19194</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.20134</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39311</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.4262</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43797</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39431</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.45234</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.46361</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.41057</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45541</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.47625</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.47715</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.43269</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44535</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.49531</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.51027</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.40842</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.46938</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.47085</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.43171</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.5224500000000001</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.51677</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.48852</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.5280900000000001</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.51897</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.51897</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.5126499999999999</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.5126499999999999</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.51644</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.52039</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.5126499999999999</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.51327</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.5284</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.52795</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.53122</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03427</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15578</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02275</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01434</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03796</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00258</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28017</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03563</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01176</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03529</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20782</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27019</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.5239400000000001</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36758</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.54343</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.43097</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.41124</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.19638</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.02472</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.49547</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.88648</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52885</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.5434600000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5980700000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.51106</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.47449</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.48697</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.4813</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.64359</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.46843</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44223</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.66551</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.57796</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.65932</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.60325</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.66095</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.62883</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.61054</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.63563</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46606</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.54274</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.60134</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52483</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.52399</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.42074</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.91128</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87215</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41655</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03587</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16208</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00283</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.05036</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.16342</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.12135</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99924</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.1491</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.05148</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.15588</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.86163</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8598899999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9604400000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.15168</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.15181</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.14571</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.39784</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.42376</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.4236</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.6080800000000001</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8996799999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.48732</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.84505</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.51891</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.62763</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.52228</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.52283</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40672</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.48948</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.53503</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.42746</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.41191</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.43168</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.6723600000000001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.44987</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.47604</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.44001</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.46303</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.46833</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.62815</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.51133</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.5089399999999999</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.61988</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.6772999999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.49988</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.52719</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.21972</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.05937</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.11166</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.09702</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.24893</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25988</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.6365</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.26643</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5104300000000001</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.9279500000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.61872</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.44974</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.55292</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.54392</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.49308</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.6845</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.40614</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.50103</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.5185299999999999</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.48799</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.48223</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.45221</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.4459</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41035</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.41051</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.55452</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.44018</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.8706699999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.02159</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.8502999999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42516</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.7965399999999999</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.61503</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45875</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.14246</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.84229</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.61322</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4913</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.62252</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.56879</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.79144</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.82935</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.60584</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.9356599999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.81875</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.61824</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.62124</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.45138</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.49031</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.57365</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.45216</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.45158</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.28464</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.40516</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.53312</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.44549</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.45472</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.44154</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.43008</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.41897</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.41039</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.39194</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.40806</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.46466</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43414</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40912</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.4338</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40098</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41367</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44581</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.45543</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45152</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.6212000000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.8057799999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.62119</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.8217300000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.86382</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.56301</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.56572</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.7865700000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.51491</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.8104199999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.96672</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.80722</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7335700000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.72322</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.02203</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.49973</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.5096700000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.44268</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.40569</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40845</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.40383</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.46039</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.6235299999999999</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.39501</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.42674</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.41074</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.23973</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20697</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.19177</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24621</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03225</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.16686</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02881</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01842</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.16884</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.18973</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03351</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05309000000000001</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27335</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23212</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24949</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.42106</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.51348</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.46232</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.41084</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42171</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.46018</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.64724</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.52454</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.55804</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.5049399999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.51363</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.45907</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4362</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.48035</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.46999</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.51797</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.44702</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.43831</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.48496</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.48986</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.57167</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.45329</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.43523</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.46628</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.43003</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.42262</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.42497</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.41745</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.41739</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.41729</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.41351</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.43032</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.40252</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.14613</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23544</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.11056</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.27564</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42521</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.44352</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.44328</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.46575</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.41928</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.47468</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.49654</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.43189</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.41742</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.47312</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.43078</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41869</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42257</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.44853</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.40446</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5132100000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.42569</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.49909</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.42431</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.42592</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.41507</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.40828</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.42252</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.41875</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.4045299999999999</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1768</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14644</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19965</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.04919</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23708</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04719</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04745000000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13385</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.00017</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17712</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22785</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15783</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24224</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.21992</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.00202</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20203</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15138</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27543</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.51616</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.45986</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.48307</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41421</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.43186</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.46282</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.44417</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.43903</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.46221</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.54035</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44588</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.43695</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41763</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.42042</v>
       </c>
     </row>
   </sheetData>
